--- a/data/trans_camb/P42C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Clase-trans_camb.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -506,8 +506,6 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,22 +517,16 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -555,16 +547,6 @@
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2012</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2012</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2023/2012</t>
         </is>
@@ -577,8 +559,6 @@
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -593,12 +573,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9,33</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -607,16 +587,6 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-9,33</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,75</t>
         </is>
@@ -631,32 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-17,76; -0,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,31; 10,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,05; -0,16</t>
+          <t>-17,76; -0,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 11,23</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-17,05; -0,16</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-4,69; 11,23</t>
+          <t>-5,31; 10,9</t>
         </is>
       </c>
     </row>
@@ -669,12 +629,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-21,71%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -683,16 +643,6 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,4%</t>
         </is>
@@ -707,32 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,56; -1,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,14; 29,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -0,48</t>
+          <t>-37,56; -1,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 28,77</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-36,74; -0,48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-9,86; 28,77</t>
+          <t>-11,14; 29,07</t>
         </is>
       </c>
     </row>
@@ -749,12 +689,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-13,55</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -763,16 +703,6 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-13,55</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
@@ -787,32 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,6; -5,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,93; 10,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,08; -5,29</t>
+          <t>-21,6; -5,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 10,41</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-22,08; -5,29</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-6,68; 10,41</t>
+          <t>-5,93; 10,97</t>
         </is>
       </c>
     </row>
@@ -825,12 +745,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-32,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -839,16 +759,6 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-32,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,6%</t>
         </is>
@@ -863,32 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-47,35; -15,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,87; 30,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,35; -13,79</t>
+          <t>-47,35; -15,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 27,99</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-47,35; -13,79</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-14,82; 27,99</t>
+          <t>-13,87; 30,03</t>
         </is>
       </c>
     </row>
@@ -905,12 +805,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-15,23</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,79</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -919,16 +819,6 @@
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-15,23</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-3,79</t>
         </is>
@@ -943,32 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,27; -6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,75; 5,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,25; -7,44</t>
+          <t>-23,27; -6,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 5,26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-23,25; -7,44</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-13,07; 5,26</t>
+          <t>-13,75; 5,74</t>
         </is>
       </c>
     </row>
@@ -981,12 +861,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-57,65%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-14,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -995,16 +875,6 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-14,35%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-57,65%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>-14,35%</t>
         </is>
@@ -1019,32 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-76,0; -25,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-44,44; 26,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,97; -32,1</t>
+          <t>-76,0; -25,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 25,52</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-76,97; -32,1</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-44,22; 25,52</t>
+          <t>-44,44; 26,85</t>
         </is>
       </c>
     </row>
@@ -1061,12 +921,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,61</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1075,16 +935,6 @@
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,88</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-7,61</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-0,88</t>
         </is>
@@ -1099,32 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,48; -3,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,24; 4,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -3,32</t>
+          <t>-11,48; -3,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,03</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-11,88; -3,32</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-5,57; 4,03</t>
+          <t>-5,24; 4,64</t>
         </is>
       </c>
     </row>
@@ -1137,12 +977,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-34,74%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,03%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1151,16 +991,6 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-4,03%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-34,74%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-4,03%</t>
         </is>
@@ -1175,32 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-48,54; -16,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,71; 23,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,81; -16,58</t>
+          <t>-48,54; -16,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 21,11</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-48,81; -16,58</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-23,29; 21,11</t>
+          <t>-21,71; 23,54</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1037,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9,1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6,05</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1231,16 +1051,6 @@
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-6,05</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-9,1</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-6,05</t>
         </is>
@@ -1255,32 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,19; -5,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,83; -1,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,58; -4,82</t>
+          <t>-13,19; -5,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -1,44</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>-12,58; -4,82</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-10,79; -1,44</t>
+          <t>-10,83; -1,87</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1093,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-58,3%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-38,77%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1307,16 +1107,6 @@
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-38,77%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-58,3%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-38,77%</t>
         </is>
@@ -1331,32 +1121,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,17; -38,2</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-61,16; -13,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-71,48; -36,36</t>
+          <t>-72,17; -38,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-62,07; -12,56</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-71,48; -36,36</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-62,07; -12,56</t>
+          <t>-61,16; -13,34</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1153,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6,74</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,62</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1387,16 +1167,6 @@
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-6,74</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-3,62</t>
         </is>
@@ -1411,32 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,68; -3,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,04; 1,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,38; -3,01</t>
+          <t>-10,68; -3,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 0,77</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>-10,38; -3,01</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-7,96; 0,77</t>
+          <t>-8,04; 1,11</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1209,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-38,07%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-20,45%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1463,16 +1223,6 @@
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-20,45%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-38,07%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>-20,45%</t>
         </is>
@@ -1487,32 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-52,89; -22,23</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-41,39; 7,63</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,88; -19,01</t>
+          <t>-52,89; -22,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 4,58</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-52,88; -19,01</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-40,96; 4,58</t>
+          <t>-41,39; 7,63</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1269,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,48</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1543,16 +1283,6 @@
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,21</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-8,48</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>-1,21</t>
         </is>
@@ -1567,32 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,68; -6,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,12; 1,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -6,32</t>
+          <t>-10,68; -6,25</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,53</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-10,95; -6,32</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-4,68; 1,53</t>
+          <t>-4,12; 1,77</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1325,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-35,45%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-5,06%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1619,16 +1339,6 @@
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-5,06%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-35,45%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>-5,06%</t>
         </is>
@@ -1643,32 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-42,28; -27,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,65; 7,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-43,35; -27,74</t>
+          <t>-42,28; -27,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 6,51</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-43,35; -27,74</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-18,37; 6,51</t>
+          <t>-16,65; 7,61</t>
         </is>
       </c>
     </row>
@@ -1680,11 +1380,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A28:A31"/>

--- a/data/trans_camb/P42C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P42C_R-Clase-trans_camb.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,93</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,76; -0,64</t>
+          <t>-17,12; -0,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 10,9</t>
+          <t>-5,58; 10,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,76; -0,64</t>
+          <t>-17,12; -0,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 10,9</t>
+          <t>-5,58; 10,14</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -657,22 +657,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,56; -1,28</t>
+          <t>-36,37; -2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 29,07</t>
+          <t>-10,86; 26,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,56; -1,28</t>
+          <t>-36,37; -2,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 29,07</t>
+          <t>-10,86; 26,25</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>1,7</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -5,91</t>
+          <t>-20,71; -4,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 10,97</t>
+          <t>-7,11; 10,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -5,91</t>
+          <t>-20,71; -4,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 10,97</t>
+          <t>-7,11; 10,26</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,35; -15,73</t>
+          <t>-45,95; -12,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 30,03</t>
+          <t>-15,55; 29,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,35; -15,73</t>
+          <t>-45,95; -12,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 30,03</t>
+          <t>-15,55; 29,22</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-3,87</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-3,87</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,27; -6,66</t>
+          <t>-23,59; -7,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 5,74</t>
+          <t>-12,37; 5,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,27; -6,66</t>
+          <t>-23,59; -7,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 5,74</t>
+          <t>-12,37; 5,87</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-14,35%</t>
+          <t>-14,66%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-14,35%</t>
+          <t>-14,66%</t>
         </is>
       </c>
     </row>
@@ -889,22 +889,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,0; -25,14</t>
+          <t>-76,85; -32,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 26,85</t>
+          <t>-41,55; 26,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,0; -25,14</t>
+          <t>-76,85; -32,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,44; 26,85</t>
+          <t>-41,55; 26,84</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-1,21</t>
         </is>
       </c>
     </row>
@@ -949,22 +949,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,48; -3,13</t>
+          <t>-11,84; -3,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 4,64</t>
+          <t>-5,94; 3,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,48; -3,13</t>
+          <t>-11,84; -3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 4,64</t>
+          <t>-5,94; 3,54</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-4,03%</t>
+          <t>-5,52%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,03%</t>
+          <t>-5,52%</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,54; -16,36</t>
+          <t>-48,72; -16,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 23,54</t>
+          <t>-24,37; 19,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,54; -16,36</t>
+          <t>-48,72; -16,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 23,54</t>
+          <t>-24,37; 19,13</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-4,0</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-4,0</t>
         </is>
       </c>
     </row>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -5,38</t>
+          <t>-12,69; -4,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -1,87</t>
+          <t>-7,93; -0,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -5,38</t>
+          <t>-12,69; -4,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -1,87</t>
+          <t>-7,93; -0,11</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-38,77%</t>
+          <t>-25,61%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-38,77%</t>
+          <t>-25,61%</t>
         </is>
       </c>
     </row>
@@ -1121,29 +1121,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,17; -38,2</t>
+          <t>-71,91; -36,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-61,16; -13,34</t>
+          <t>-45,35; -1,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-72,17; -38,2</t>
+          <t>-71,91; -36,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-61,16; -13,34</t>
+          <t>-45,35; -1,03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-3,99</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>-3,99</t>
         </is>
       </c>
     </row>
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -3,61</t>
+          <t>-10,39; -2,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 1,11</t>
+          <t>-8,06; 0,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -3,61</t>
+          <t>-10,39; -2,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 1,11</t>
+          <t>-8,06; 0,67</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-20,45%</t>
+          <t>-22,56%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-20,45%</t>
+          <t>-22,56%</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1237,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,89; -22,23</t>
+          <t>-52,81; -17,55</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-41,39; 7,63</t>
+          <t>-40,82; 5,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,89; -22,23</t>
+          <t>-52,81; -17,55</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,39; 7,63</t>
+          <t>-40,82; 5,17</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-0,14</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1297,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -6,25</t>
+          <t>-10,71; -6,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,77</t>
+          <t>-2,45; 2,26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -6,25</t>
+          <t>-10,71; -6,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,77</t>
+          <t>-2,45; 2,26</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-5,06%</t>
+          <t>-0,6%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-5,06%</t>
+          <t>-0,6%</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-42,28; -27,44</t>
+          <t>-42,54; -28,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 7,61</t>
+          <t>-9,64; 10,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,28; -27,44</t>
+          <t>-42,54; -28,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 7,61</t>
+          <t>-9,64; 10,08</t>
         </is>
       </c>
     </row>
